--- a/199.022/source_data/199.022_par_data.xlsx
+++ b/199.022/source_data/199.022_par_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interainc-my.sharepoint.com/personal/mearll_intera_com/Documents/Models/DWR_Contract/Long_term_sites_data/00_Model_Input_files/199.022/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jwhite/Dev/1D_CSUB/199.022/source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{D1A893F4-564B-4D6A-9172-42423F7ECD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BDF7739-ABDC-450B-BF4A-AF6180251FEC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF048CC2-10DE-F844-8469-450BEB77C832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6195" yWindow="360" windowWidth="15360" windowHeight="13785" xr2:uid="{5DFCA8DB-E838-45AE-8EA2-ACBA3F797179}"/>
+    <workbookView xWindow="6200" yWindow="680" windowWidth="18560" windowHeight="13780" xr2:uid="{5DFCA8DB-E838-45AE-8EA2-ACBA3F797179}"/>
   </bookViews>
   <sheets>
     <sheet name="199.022" sheetId="1" r:id="rId1"/>
@@ -1745,20 +1745,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52A3A2E-15BE-48BB-8BE7-324FA39E0EFB}">
   <dimension ref="B1:T33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="67.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="67.83203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
         <v>46</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1930,13 +1930,13 @@
         <v>41</v>
       </c>
       <c r="K7" s="6">
-        <v>6.2335960000000001E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="L7" s="6">
-        <v>1.8035187585000001E-2</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M7" s="6">
-        <v>1.8035187585000001E-2</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="R7" t="s">
         <v>15</v>
@@ -1945,20 +1945,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="J8" t="s">
         <v>42</v>
       </c>
       <c r="K8" s="6">
-        <v>3.2808400000000003E-5</v>
+        <v>1E-8</v>
       </c>
       <c r="L8" s="6">
-        <v>9.1107778506000002E-5</v>
+        <v>1E-8</v>
       </c>
       <c r="M8" s="6">
-        <v>9.1107778506000002E-5</v>
+        <v>1E-8</v>
       </c>
       <c r="R8" t="s">
         <v>16</v>
@@ -1967,7 +1967,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -1978,13 +1978,13 @@
         <v>43</v>
       </c>
       <c r="K9">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L9">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M9">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R9" t="s">
         <v>17</v>
@@ -1996,7 +1996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>
       <c r="J10" t="s">
         <v>44</v>
@@ -2017,7 +2017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
       <c r="J11" t="s">
         <v>45</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="J12" t="s">
@@ -2056,7 +2056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -2075,7 +2075,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
       <c r="G14" s="5"/>
@@ -2086,7 +2086,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
       <c r="G15" s="5"/>
@@ -2097,26 +2097,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E16" s="5"/>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E19" s="6"/>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
         <v>47</v>
       </c>
@@ -2125,13 +2125,30 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="43f450d6-c7e2-47fd-a9bf-53824f1809db" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD3086B75032B64DB34150BB0186A2C3" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6f811fed7ec76b69a2fe73333b0881e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="43f450d6-c7e2-47fd-a9bf-53824f1809db" xmlns:ns4="f05a7dec-63b6-4d32-83ea-1f7900633414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae12a500b6a41a23147cb20202262367" ns3:_="" ns4:_="">
     <xsd:import namespace="43f450d6-c7e2-47fd-a9bf-53824f1809db"/>
@@ -2370,24 +2387,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{508EEB76-B9F2-4694-B418-32A4E14BE931}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f05a7dec-63b6-4d32-83ea-1f7900633414"/>
+    <ds:schemaRef ds:uri="43f450d6-c7e2-47fd-a9bf-53824f1809db"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="43f450d6-c7e2-47fd-a9bf-53824f1809db" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{153C8F86-C431-450F-BF06-3F0BF1A8C94F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57806B79-A01B-4461-9D99-63D249F79A15}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2404,29 +2429,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{153C8F86-C431-450F-BF06-3F0BF1A8C94F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{508EEB76-B9F2-4694-B418-32A4E14BE931}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f05a7dec-63b6-4d32-83ea-1f7900633414"/>
-    <ds:schemaRef ds:uri="43f450d6-c7e2-47fd-a9bf-53824f1809db"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>